--- a/data/trans_orig/IP07_C11_2023-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/IP07_C11_2023-Provincia-trans_orig.xlsx
@@ -535,13 +535,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según la frecuencia de tener problemas para dormir en 2023 (tasa de respuesta: 100,0%)</t>
+          <t>Menores según la frecuencia de tener problemas para dormir, percibida por el/la menor en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -552,7 +552,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -1172,64 +1172,64 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>657</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>1174</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>1147</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>741</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
           <t>—%</t>
@@ -1247,7 +1247,7 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>1915</t>
+          <t>1804</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
@@ -1285,57 +1285,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>657</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>657</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>657</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>1174</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>1174</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>1174</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>741</t>
+          <t>1147</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>741</t>
+          <t>1147</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>741</t>
+          <t>1147</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1360,17 +1360,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>1915</t>
+          <t>1804</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1915</t>
+          <t>1804</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1915</t>
+          <t>1804</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1515,72 +1515,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>2212</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>6628</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>3,58%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>10,71%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2362</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>721</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>6328</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>6,14%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>16,45%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1590,32 +1590,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>2212</t>
+          <t>2362</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>112</t>
+          <t>711</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>7037</t>
+          <t>6907</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>0,09%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>5,88%</t>
+          <t>7,44%</t>
         </is>
       </c>
     </row>
@@ -1628,72 +1628,72 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>416</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>2292</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>0,67%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>3,7%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>359</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2030</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>5,27%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1703,7 +1703,7 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>416</t>
+          <t>359</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
@@ -1713,12 +1713,12 @@
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>2186</t>
+          <t>1727</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
@@ -1728,7 +1728,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,86%</t>
         </is>
       </c>
     </row>
@@ -1741,72 +1741,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>1889</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>7412</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>3,47%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>13,63%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>29986</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>3745</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>51915</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>48,48%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>6,05%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>83,93%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>1918</t>
+          <t>5981</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2093</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>6164</t>
+          <t>14673</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>15,54%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>5,44%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>10,65%</t>
+          <t>38,13%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1816,32 +1816,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>31903</t>
+          <t>7870</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>4848</t>
+          <t>3433</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>74582</t>
+          <t>18297</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>26,65%</t>
+          <t>8,47%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>62,3%</t>
+          <t>19,7%</t>
         </is>
       </c>
     </row>
@@ -1854,72 +1854,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>52502</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>46979</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>54391</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>96,53%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>86,37%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>39</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>29244</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>9395</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>53815</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>47,28%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>15,19%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>87,0%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>55942</t>
+          <t>29780</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>51696</t>
+          <t>21784</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>57860</t>
+          <t>34109</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>96,69%</t>
+          <t>77,39%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>89,35%</t>
+          <t>56,61%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>88,64%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1929,32 +1929,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>85186</t>
+          <t>82281</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>45024</t>
+          <t>71947</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>111784</t>
+          <t>87306</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>71,16%</t>
+          <t>88,6%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>37,61%</t>
+          <t>77,47%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>93,37%</t>
+          <t>94,01%</t>
         </is>
       </c>
     </row>
@@ -1967,57 +1967,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>54391</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>54391</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>54391</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>48</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>61857</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>61857</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>61857</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>53</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>57860</t>
+          <t>38481</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>57860</t>
+          <t>38481</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>57860</t>
+          <t>38481</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2042,17 +2042,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>119717</t>
+          <t>92871</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>119717</t>
+          <t>92871</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>119717</t>
+          <t>92871</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2197,47 +2197,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>1785</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>449</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>5037</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>7,73%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>1,94%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>21,83%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>590</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>3193</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>2,83%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>15,3%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>2049</t>
+          <t>592</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
@@ -2247,12 +2247,12 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>5333</t>
+          <t>3824</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>8,06%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
@@ -2262,7 +2262,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>20,98%</t>
+          <t>18,34%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2272,32 +2272,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>2639</t>
+          <t>2377</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>754</t>
+          <t>673</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6788</t>
+          <t>5961</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>5,7%</t>
+          <t>5,41%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>14,67%</t>
+          <t>13,57%</t>
         </is>
       </c>
     </row>
@@ -2310,72 +2310,72 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>622</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>3142</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>2,98%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>15,06%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>611</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3162</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>15,16%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2385,7 +2385,7 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>622</t>
+          <t>611</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
@@ -2395,12 +2395,12 @@
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>3545</t>
+          <t>3356</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
@@ -2410,7 +2410,7 @@
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>7,66%</t>
+          <t>7,64%</t>
         </is>
       </c>
     </row>
@@ -2423,72 +2423,72 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>1655</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>5626</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>7,17%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>24,38%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>2469</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>562</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>5066</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>11,83%</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>2,69%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>24,27%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>1986</t>
+          <t>2413</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>626</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>7302</t>
+          <t>5642</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>7,81%</t>
+          <t>11,57%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>28,73%</t>
+          <t>27,06%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2498,22 +2498,22 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>4455</t>
+          <t>4068</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1808</t>
+          <t>1717</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>8785</t>
+          <t>8828</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>9,62%</t>
+          <t>9,26%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
@@ -2523,7 +2523,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>18,98%</t>
+          <t>20,1%</t>
         </is>
       </c>
     </row>
@@ -2536,72 +2536,72 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>19638</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>15924</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>21726</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>85,09%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>69,0%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>94,14%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>28</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>17188</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>14017</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>19588</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>82,36%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>67,17%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>93,86%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>21383</t>
+          <t>17234</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>17063</t>
+          <t>13971</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>23974</t>
+          <t>19534</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>84,12%</t>
+          <t>82,66%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>67,13%</t>
+          <t>67,01%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>94,32%</t>
+          <t>93,69%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2611,32 +2611,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>38571</t>
+          <t>36873</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>32961</t>
+          <t>32078</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>42173</t>
+          <t>40086</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>83,33%</t>
+          <t>83,94%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>71,21%</t>
+          <t>73,02%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>91,11%</t>
+          <t>91,25%</t>
         </is>
       </c>
     </row>
@@ -2649,57 +2649,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>23078</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>23078</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>23078</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>34</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>20869</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>20869</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>20869</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>25418</t>
+          <t>20850</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>25418</t>
+          <t>20850</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>25418</t>
+          <t>20850</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2724,17 +2724,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>46287</t>
+          <t>43928</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>46287</t>
+          <t>43928</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>46287</t>
+          <t>43928</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2879,82 +2879,82 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1526</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>7704</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>8,75%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>44,2%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q23" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>1516</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>8421</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>7,68%</t>
-        </is>
-      </c>
-      <c r="O23" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P23" s="2" t="inlineStr">
-        <is>
-          <t>42,64%</t>
-        </is>
-      </c>
-      <c r="Q23" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>1516</t>
+          <t>1526</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
@@ -2964,12 +2964,12 @@
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>7973</t>
+          <t>7040</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>6,77%</t>
+          <t>7,49%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
@@ -2979,7 +2979,7 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>35,59%</t>
+          <t>34,56%</t>
         </is>
       </c>
     </row>
@@ -3105,74 +3105,74 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>1193</t>
-        </is>
-      </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>2649</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
-        <is>
-          <t>45,04%</t>
-        </is>
-      </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="I25" s="2" t="inlineStr">
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>1471</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>2938</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>50,07%</t>
+        </is>
+      </c>
+      <c r="O25" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K25" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L25" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N25" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="O25" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P25" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="Q25" s="2" t="inlineStr">
         <is>
           <t>2</t>
@@ -3180,7 +3180,7 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>1193</t>
+          <t>1471</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
@@ -3190,12 +3190,12 @@
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>5456</t>
+          <t>6606</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>7,22%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
@@ -3205,7 +3205,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>24,36%</t>
+          <t>32,43%</t>
         </is>
       </c>
     </row>
@@ -3218,74 +3218,74 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>15905</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>9786</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>17431</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>91,25%</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>56,14%</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>1456</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>2649</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>54,96%</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>1467</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>2938</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>49,93%</t>
+        </is>
+      </c>
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>18234</t>
-        </is>
-      </c>
-      <c r="L26" s="2" t="inlineStr">
-        <is>
-          <t>11329</t>
-        </is>
-      </c>
-      <c r="M26" s="2" t="inlineStr">
-        <is>
-          <t>19750</t>
-        </is>
-      </c>
-      <c r="N26" s="2" t="inlineStr">
-        <is>
-          <t>92,32%</t>
-        </is>
-      </c>
-      <c r="O26" s="2" t="inlineStr">
-        <is>
-          <t>57,36%</t>
-        </is>
-      </c>
-      <c r="P26" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q26" s="2" t="inlineStr">
         <is>
           <t>9</t>
@@ -3293,27 +3293,27 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>19690</t>
+          <t>17372</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>13837</t>
+          <t>11463</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>22399</t>
+          <t>20369</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>87,9%</t>
+          <t>85,29%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>61,78%</t>
+          <t>56,27%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -3331,57 +3331,57 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>17431</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>17431</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>17431</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
-        <is>
-          <t>2649</t>
-        </is>
-      </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>2649</t>
-        </is>
-      </c>
-      <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t>2649</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>19750</t>
+          <t>2938</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>19750</t>
+          <t>2938</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>19750</t>
+          <t>2938</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3406,17 +3406,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>22399</t>
+          <t>20369</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>22399</t>
+          <t>20369</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>22399</t>
+          <t>20369</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3448,47 +3448,47 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>1216</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>3798</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>6,0%</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>18,72%</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>456</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>2743</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>3,1%</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>18,66%</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>1165</t>
+          <t>490</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
@@ -3498,12 +3498,12 @@
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>3603</t>
+          <t>2044</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>5,83%</t>
+          <t>3,15%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
@@ -3513,7 +3513,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>18,03%</t>
+          <t>13,12%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3523,32 +3523,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>1621</t>
+          <t>1706</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>456</t>
+          <t>487</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>4599</t>
+          <t>4577</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>4,76%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>13,26%</t>
+          <t>12,76%</t>
         </is>
       </c>
     </row>
@@ -3561,72 +3561,72 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
-        <is>
-          <t>570</t>
-        </is>
-      </c>
-      <c r="E29" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>2550</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
-        <is>
-          <t>3,88%</t>
-        </is>
-      </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>17,35%</t>
-        </is>
-      </c>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>609</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3019</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>3,91%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>19,39%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>570</t>
+          <t>609</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
@@ -3646,12 +3646,12 @@
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>2624</t>
+          <t>3058</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
@@ -3661,7 +3661,7 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>7,57%</t>
+          <t>8,53%</t>
         </is>
       </c>
     </row>
@@ -3674,82 +3674,82 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1201</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3998</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>5,92%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>19,71%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N30" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O30" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P30" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q30" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K30" s="2" t="inlineStr">
-        <is>
-          <t>1223</t>
-        </is>
-      </c>
-      <c r="L30" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M30" s="2" t="inlineStr">
-        <is>
-          <t>3751</t>
-        </is>
-      </c>
-      <c r="N30" s="2" t="inlineStr">
-        <is>
-          <t>6,12%</t>
-        </is>
-      </c>
-      <c r="O30" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P30" s="2" t="inlineStr">
-        <is>
-          <t>18,77%</t>
-        </is>
-      </c>
-      <c r="Q30" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>1223</t>
+          <t>1201</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
@@ -3759,12 +3759,12 @@
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>3950</t>
+          <t>4083</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
@@ -3787,72 +3787,72 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>3330</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>1291</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>6850</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>16,42%</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>6,37%</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>33,77%</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D31" s="2" t="inlineStr">
-        <is>
-          <t>2342</t>
-        </is>
-      </c>
-      <c r="E31" s="2" t="inlineStr">
-        <is>
-          <t>573</t>
-        </is>
-      </c>
-      <c r="F31" s="2" t="inlineStr">
-        <is>
-          <t>5153</t>
-        </is>
-      </c>
-      <c r="G31" s="2" t="inlineStr">
-        <is>
-          <t>15,93%</t>
-        </is>
-      </c>
-      <c r="H31" s="2" t="inlineStr">
-        <is>
-          <t>3,9%</t>
-        </is>
-      </c>
-      <c r="I31" s="2" t="inlineStr">
-        <is>
-          <t>35,06%</t>
-        </is>
-      </c>
-      <c r="J31" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>3334</t>
+          <t>2404</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>1296</t>
+          <t>770</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>7154</t>
+          <t>5833</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>16,69%</t>
+          <t>15,44%</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>6,49%</t>
+          <t>4,94%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>35,8%</t>
+          <t>37,46%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3862,32 +3862,32 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>5676</t>
+          <t>5734</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>2908</t>
+          <t>2847</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>9590</t>
+          <t>10261</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t>16,37%</t>
+          <t>15,99%</t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>8,38%</t>
+          <t>7,94%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>27,65%</t>
+          <t>28,62%</t>
         </is>
       </c>
     </row>
@@ -3900,72 +3900,72 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>14537</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>10786</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>17011</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>71,67%</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>53,17%</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>83,86%</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
           <t>21</t>
         </is>
       </c>
-      <c r="D32" s="2" t="inlineStr">
-        <is>
-          <t>11331</t>
-        </is>
-      </c>
-      <c r="E32" s="2" t="inlineStr">
-        <is>
-          <t>8232</t>
-        </is>
-      </c>
-      <c r="F32" s="2" t="inlineStr">
-        <is>
-          <t>13225</t>
-        </is>
-      </c>
-      <c r="G32" s="2" t="inlineStr">
-        <is>
-          <t>77,09%</t>
-        </is>
-      </c>
-      <c r="H32" s="2" t="inlineStr">
-        <is>
-          <t>56,0%</t>
-        </is>
-      </c>
-      <c r="I32" s="2" t="inlineStr">
-        <is>
-          <t>89,98%</t>
-        </is>
-      </c>
-      <c r="J32" s="2" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
+          <t>12070</t>
+        </is>
+      </c>
+      <c r="L32" s="2" t="inlineStr">
+        <is>
+          <t>9160</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="inlineStr">
+        <is>
           <t>14260</t>
         </is>
       </c>
-      <c r="L32" s="2" t="inlineStr">
-        <is>
-          <t>10592</t>
-        </is>
-      </c>
-      <c r="M32" s="2" t="inlineStr">
-        <is>
-          <t>16973</t>
-        </is>
-      </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>71,36%</t>
+          <t>77,5%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>53,01%</t>
+          <t>58,81%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>84,94%</t>
+          <t>91,56%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3975,32 +3975,32 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>25590</t>
+          <t>26608</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>21370</t>
+          <t>22212</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>29033</t>
+          <t>30185</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>73,79%</t>
+          <t>74,2%</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>61,62%</t>
+          <t>61,94%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>83,72%</t>
+          <t>84,18%</t>
         </is>
       </c>
     </row>
@@ -4013,57 +4013,57 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>20285</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>20285</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>20285</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr">
+        <is>
           <t>27</t>
         </is>
       </c>
-      <c r="D33" s="2" t="inlineStr">
-        <is>
-          <t>14698</t>
-        </is>
-      </c>
-      <c r="E33" s="2" t="inlineStr">
-        <is>
-          <t>14698</t>
-        </is>
-      </c>
-      <c r="F33" s="2" t="inlineStr">
-        <is>
-          <t>14698</t>
-        </is>
-      </c>
-      <c r="G33" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H33" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I33" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J33" s="2" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>19982</t>
+          <t>15574</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>19982</t>
+          <t>15574</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>19982</t>
+          <t>15574</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4088,17 +4088,17 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>34680</t>
+          <t>35859</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>34680</t>
+          <t>35859</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>34680</t>
+          <t>35859</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4469,72 +4469,72 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>3099</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>1167</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>6625</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>15,93%</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>6,0%</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>34,06%</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D37" s="2" t="inlineStr">
-        <is>
-          <t>1227</t>
-        </is>
-      </c>
-      <c r="E37" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F37" s="2" t="inlineStr">
-        <is>
-          <t>3820</t>
-        </is>
-      </c>
-      <c r="G37" s="2" t="inlineStr">
-        <is>
-          <t>6,66%</t>
-        </is>
-      </c>
-      <c r="H37" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="I37" s="2" t="inlineStr">
-        <is>
-          <t>20,73%</t>
-        </is>
-      </c>
-      <c r="J37" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>3417</t>
+          <t>1236</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>1326</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>7381</t>
+          <t>3780</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>16,32%</t>
+          <t>6,38%</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>6,33%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>35,25%</t>
+          <t>19,52%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4544,32 +4544,32 @@
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t>4643</t>
+          <t>4335</t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>2014</t>
+          <t>1954</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>8516</t>
+          <t>8358</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
-          <t>11,8%</t>
+          <t>11,17%</t>
         </is>
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>5,12%</t>
+          <t>5,03%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>21,63%</t>
+          <t>21,53%</t>
         </is>
       </c>
     </row>
@@ -4582,74 +4582,74 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>16352</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>12826</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>18284</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>84,07%</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>65,94%</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>94,0%</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr">
+        <is>
           <t>29</t>
         </is>
       </c>
-      <c r="D38" s="2" t="inlineStr">
-        <is>
-          <t>17198</t>
-        </is>
-      </c>
-      <c r="E38" s="2" t="inlineStr">
-        <is>
-          <t>14605</t>
-        </is>
-      </c>
-      <c r="F38" s="2" t="inlineStr">
-        <is>
-          <t>18425</t>
-        </is>
-      </c>
-      <c r="G38" s="2" t="inlineStr">
-        <is>
-          <t>93,34%</t>
-        </is>
-      </c>
-      <c r="H38" s="2" t="inlineStr">
-        <is>
-          <t>79,27%</t>
-        </is>
-      </c>
-      <c r="I38" s="2" t="inlineStr">
+      <c r="K38" s="2" t="inlineStr">
+        <is>
+          <t>18127</t>
+        </is>
+      </c>
+      <c r="L38" s="2" t="inlineStr">
+        <is>
+          <t>15583</t>
+        </is>
+      </c>
+      <c r="M38" s="2" t="inlineStr">
+        <is>
+          <t>19363</t>
+        </is>
+      </c>
+      <c r="N38" s="2" t="inlineStr">
+        <is>
+          <t>93,62%</t>
+        </is>
+      </c>
+      <c r="O38" s="2" t="inlineStr">
+        <is>
+          <t>80,48%</t>
+        </is>
+      </c>
+      <c r="P38" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J38" s="2" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="K38" s="2" t="inlineStr">
-        <is>
-          <t>17523</t>
-        </is>
-      </c>
-      <c r="L38" s="2" t="inlineStr">
-        <is>
-          <t>13559</t>
-        </is>
-      </c>
-      <c r="M38" s="2" t="inlineStr">
-        <is>
-          <t>19614</t>
-        </is>
-      </c>
-      <c r="N38" s="2" t="inlineStr">
-        <is>
-          <t>83,68%</t>
-        </is>
-      </c>
-      <c r="O38" s="2" t="inlineStr">
-        <is>
-          <t>64,75%</t>
-        </is>
-      </c>
-      <c r="P38" s="2" t="inlineStr">
-        <is>
-          <t>93,67%</t>
-        </is>
-      </c>
       <c r="Q38" s="2" t="inlineStr">
         <is>
           <t>54</t>
@@ -4657,32 +4657,32 @@
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t>34722</t>
+          <t>34479</t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>30849</t>
+          <t>30456</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>37351</t>
+          <t>36860</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
         <is>
-          <t>88,2%</t>
+          <t>88,83%</t>
         </is>
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>78,37%</t>
+          <t>78,47%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>94,88%</t>
+          <t>94,97%</t>
         </is>
       </c>
     </row>
@@ -4695,57 +4695,57 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>19451</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>19451</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>19451</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="inlineStr">
+        <is>
           <t>31</t>
         </is>
       </c>
-      <c r="D39" s="2" t="inlineStr">
-        <is>
-          <t>18425</t>
-        </is>
-      </c>
-      <c r="E39" s="2" t="inlineStr">
-        <is>
-          <t>18425</t>
-        </is>
-      </c>
-      <c r="F39" s="2" t="inlineStr">
-        <is>
-          <t>18425</t>
-        </is>
-      </c>
-      <c r="G39" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H39" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I39" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J39" s="2" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>20940</t>
+          <t>19363</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>20940</t>
+          <t>19363</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>20940</t>
+          <t>19363</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -4770,17 +4770,17 @@
       </c>
       <c r="R39" s="2" t="inlineStr">
         <is>
-          <t>39365</t>
+          <t>38814</t>
         </is>
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>39365</t>
+          <t>38814</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>39365</t>
+          <t>38814</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -4812,82 +4812,82 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>357</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1924</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>4,04%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K40" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L40" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M40" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N40" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O40" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P40" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q40" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K40" s="2" t="inlineStr">
-        <is>
-          <t>427</t>
-        </is>
-      </c>
-      <c r="L40" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M40" s="2" t="inlineStr">
-        <is>
-          <t>2166</t>
-        </is>
-      </c>
-      <c r="N40" s="2" t="inlineStr">
-        <is>
-          <t>0,92%</t>
-        </is>
-      </c>
-      <c r="O40" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P40" s="2" t="inlineStr">
-        <is>
-          <t>4,69%</t>
-        </is>
-      </c>
-      <c r="Q40" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="R40" s="2" t="inlineStr">
         <is>
-          <t>427</t>
+          <t>357</t>
         </is>
       </c>
       <c r="S40" s="2" t="inlineStr">
@@ -4897,12 +4897,12 @@
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>1828</t>
+          <t>1860</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="V40" s="2" t="inlineStr">
@@ -4912,7 +4912,7 @@
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,43%</t>
         </is>
       </c>
     </row>
@@ -4925,47 +4925,47 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>1788</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>6589</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>3,76%</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>13,86%</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D41" s="2" t="inlineStr">
-        <is>
-          <t>717</t>
-        </is>
-      </c>
-      <c r="E41" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F41" s="2" t="inlineStr">
-        <is>
-          <t>3691</t>
-        </is>
-      </c>
-      <c r="G41" s="2" t="inlineStr">
-        <is>
-          <t>2,63%</t>
-        </is>
-      </c>
-      <c r="H41" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="I41" s="2" t="inlineStr">
-        <is>
-          <t>13,52%</t>
-        </is>
-      </c>
-      <c r="J41" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>1715</t>
+          <t>801</t>
         </is>
       </c>
       <c r="L41" s="2" t="inlineStr">
@@ -4975,12 +4975,12 @@
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>6097</t>
+          <t>3413</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="O41" s="2" t="inlineStr">
@@ -4990,7 +4990,7 @@
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>13,21%</t>
+          <t>11,83%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5000,32 +5000,32 @@
       </c>
       <c r="R41" s="2" t="inlineStr">
         <is>
-          <t>2432</t>
+          <t>2589</t>
         </is>
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>728</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>6292</t>
+          <t>6424</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>8,57%</t>
+          <t>8,41%</t>
         </is>
       </c>
     </row>
@@ -5038,72 +5038,72 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>881</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>5157</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>1,85%</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>10,84%</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D42" s="2" t="inlineStr">
-        <is>
-          <t>3809</t>
-        </is>
-      </c>
-      <c r="E42" s="2" t="inlineStr">
-        <is>
-          <t>1476</t>
-        </is>
-      </c>
-      <c r="F42" s="2" t="inlineStr">
-        <is>
-          <t>8538</t>
-        </is>
-      </c>
-      <c r="G42" s="2" t="inlineStr">
-        <is>
-          <t>13,96%</t>
-        </is>
-      </c>
-      <c r="H42" s="2" t="inlineStr">
-        <is>
-          <t>5,41%</t>
-        </is>
-      </c>
-      <c r="I42" s="2" t="inlineStr">
-        <is>
-          <t>31,28%</t>
-        </is>
-      </c>
-      <c r="J42" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>882</t>
+          <t>4001</t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1565</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>3913</t>
+          <t>8609</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>13,87%</t>
         </is>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>5,43%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>8,48%</t>
+          <t>29,85%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5113,17 +5113,17 @@
       </c>
       <c r="R42" s="2" t="inlineStr">
         <is>
-          <t>4691</t>
+          <t>4883</t>
         </is>
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>1703</t>
+          <t>2053</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>10794</t>
+          <t>11748</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>14,7%</t>
+          <t>15,38%</t>
         </is>
       </c>
     </row>
@@ -5151,72 +5151,72 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>18056</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>11281</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>26434</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>37,97%</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>23,72%</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>55,58%</t>
+        </is>
+      </c>
+      <c r="J43" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D43" s="2" t="inlineStr">
-        <is>
-          <t>2736</t>
-        </is>
-      </c>
-      <c r="E43" s="2" t="inlineStr">
-        <is>
-          <t>746</t>
-        </is>
-      </c>
-      <c r="F43" s="2" t="inlineStr">
-        <is>
-          <t>6005</t>
-        </is>
-      </c>
-      <c r="G43" s="2" t="inlineStr">
+      <c r="K43" s="2" t="inlineStr">
+        <is>
+          <t>2890</t>
+        </is>
+      </c>
+      <c r="L43" s="2" t="inlineStr">
+        <is>
+          <t>854</t>
+        </is>
+      </c>
+      <c r="M43" s="2" t="inlineStr">
+        <is>
+          <t>6910</t>
+        </is>
+      </c>
+      <c r="N43" s="2" t="inlineStr">
         <is>
           <t>10,02%</t>
         </is>
       </c>
-      <c r="H43" s="2" t="inlineStr">
-        <is>
-          <t>2,73%</t>
-        </is>
-      </c>
-      <c r="I43" s="2" t="inlineStr">
-        <is>
-          <t>22,0%</t>
-        </is>
-      </c>
-      <c r="J43" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="K43" s="2" t="inlineStr">
-        <is>
-          <t>17351</t>
-        </is>
-      </c>
-      <c r="L43" s="2" t="inlineStr">
-        <is>
-          <t>10943</t>
-        </is>
-      </c>
-      <c r="M43" s="2" t="inlineStr">
-        <is>
-          <t>25150</t>
-        </is>
-      </c>
-      <c r="N43" s="2" t="inlineStr">
-        <is>
-          <t>37,61%</t>
-        </is>
-      </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>23,72%</t>
+          <t>2,96%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>54,51%</t>
+          <t>23,96%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5226,32 +5226,32 @@
       </c>
       <c r="R43" s="2" t="inlineStr">
         <is>
-          <t>20087</t>
+          <t>20946</t>
         </is>
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>13010</t>
+          <t>13792</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>30511</t>
+          <t>32095</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
         <is>
-          <t>27,35%</t>
+          <t>27,42%</t>
         </is>
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>17,72%</t>
+          <t>18,05%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>41,55%</t>
+          <t>42,01%</t>
         </is>
       </c>
     </row>
@@ -5264,72 +5264,72 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>26475</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>18449</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>33309</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>55,67%</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>38,79%</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>70,04%</t>
+        </is>
+      </c>
+      <c r="J44" s="2" t="inlineStr">
+        <is>
           <t>27</t>
         </is>
       </c>
-      <c r="D44" s="2" t="inlineStr">
-        <is>
-          <t>20034</t>
-        </is>
-      </c>
-      <c r="E44" s="2" t="inlineStr">
-        <is>
-          <t>15130</t>
-        </is>
-      </c>
-      <c r="F44" s="2" t="inlineStr">
-        <is>
-          <t>23187</t>
-        </is>
-      </c>
-      <c r="G44" s="2" t="inlineStr">
-        <is>
-          <t>73,4%</t>
-        </is>
-      </c>
-      <c r="H44" s="2" t="inlineStr">
-        <is>
-          <t>55,43%</t>
-        </is>
-      </c>
-      <c r="I44" s="2" t="inlineStr">
-        <is>
-          <t>84,95%</t>
-        </is>
-      </c>
-      <c r="J44" s="2" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>25766</t>
+          <t>21151</t>
         </is>
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>18325</t>
+          <t>16110</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>32199</t>
+          <t>24709</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
-          <t>55,84%</t>
+          <t>73,33%</t>
         </is>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>39,72%</t>
+          <t>55,85%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>69,78%</t>
+          <t>85,67%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5339,32 +5339,32 @@
       </c>
       <c r="R44" s="2" t="inlineStr">
         <is>
-          <t>45799</t>
+          <t>47626</t>
         </is>
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>36256</t>
+          <t>38541</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>53722</t>
+          <t>55468</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
         <is>
-          <t>62,37%</t>
+          <t>62,34%</t>
         </is>
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>49,37%</t>
+          <t>50,45%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>73,15%</t>
+          <t>72,6%</t>
         </is>
       </c>
     </row>
@@ -5377,57 +5377,57 @@
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>47558</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>47558</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>47558</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J45" s="2" t="inlineStr">
+        <is>
           <t>37</t>
         </is>
       </c>
-      <c r="D45" s="2" t="inlineStr">
-        <is>
-          <t>27295</t>
-        </is>
-      </c>
-      <c r="E45" s="2" t="inlineStr">
-        <is>
-          <t>27295</t>
-        </is>
-      </c>
-      <c r="F45" s="2" t="inlineStr">
-        <is>
-          <t>27295</t>
-        </is>
-      </c>
-      <c r="G45" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H45" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I45" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J45" s="2" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>46141</t>
+          <t>28843</t>
         </is>
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>46141</t>
+          <t>28843</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>46141</t>
+          <t>28843</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -5452,17 +5452,17 @@
       </c>
       <c r="R45" s="2" t="inlineStr">
         <is>
-          <t>73436</t>
+          <t>76401</t>
         </is>
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t>73436</t>
+          <t>76401</t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>73436</t>
+          <t>76401</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
@@ -5494,72 +5494,72 @@
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>2937</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>943</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>7972</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>3,37%</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>1,08%</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>9,14%</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D46" s="2" t="inlineStr">
-        <is>
-          <t>4939</t>
-        </is>
-      </c>
-      <c r="E46" s="2" t="inlineStr">
-        <is>
-          <t>1838</t>
-        </is>
-      </c>
-      <c r="F46" s="2" t="inlineStr">
-        <is>
-          <t>10800</t>
-        </is>
-      </c>
-      <c r="G46" s="2" t="inlineStr">
-        <is>
-          <t>7,78%</t>
-        </is>
-      </c>
-      <c r="H46" s="2" t="inlineStr">
-        <is>
-          <t>2,89%</t>
-        </is>
-      </c>
-      <c r="I46" s="2" t="inlineStr">
-        <is>
-          <t>17,01%</t>
-        </is>
-      </c>
-      <c r="J46" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>2784</t>
+          <t>6239</t>
         </is>
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>869</t>
+          <t>2648</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>7477</t>
+          <t>14517</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>8,86%</t>
         </is>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>3,76%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>9,2%</t>
+          <t>20,62%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5569,32 +5569,32 @@
       </c>
       <c r="R46" s="2" t="inlineStr">
         <is>
-          <t>7723</t>
+          <t>9175</t>
         </is>
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>3615</t>
+          <t>4401</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>14214</t>
+          <t>18215</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>5,82%</t>
         </is>
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>9,81%</t>
+          <t>11,55%</t>
         </is>
       </c>
     </row>
@@ -5612,7 +5612,7 @@
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>1564</t>
+          <t>1984</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
@@ -5622,12 +5622,12 @@
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>5295</t>
+          <t>6098</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
@@ -5637,7 +5637,7 @@
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>8,34%</t>
+          <t>6,99%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -5647,7 +5647,7 @@
       </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
-          <t>1919</t>
+          <t>1738</t>
         </is>
       </c>
       <c r="L47" s="2" t="inlineStr">
@@ -5657,57 +5657,57 @@
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>5804</t>
+          <t>5731</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
+          <t>2,47%</t>
+        </is>
+      </c>
+      <c r="O47" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="P47" s="2" t="inlineStr">
+        <is>
+          <t>8,14%</t>
+        </is>
+      </c>
+      <c r="Q47" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="R47" s="2" t="inlineStr">
+        <is>
+          <t>3722</t>
+        </is>
+      </c>
+      <c r="S47" s="2" t="inlineStr">
+        <is>
+          <t>955</t>
+        </is>
+      </c>
+      <c r="T47" s="2" t="inlineStr">
+        <is>
+          <t>8593</t>
+        </is>
+      </c>
+      <c r="U47" s="2" t="inlineStr">
+        <is>
           <t>2,36%</t>
         </is>
       </c>
-      <c r="O47" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P47" s="2" t="inlineStr">
-        <is>
-          <t>7,14%</t>
-        </is>
-      </c>
-      <c r="Q47" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="R47" s="2" t="inlineStr">
-        <is>
-          <t>3483</t>
-        </is>
-      </c>
-      <c r="S47" s="2" t="inlineStr">
-        <is>
-          <t>1021</t>
-        </is>
-      </c>
-      <c r="T47" s="2" t="inlineStr">
-        <is>
-          <t>8079</t>
-        </is>
-      </c>
-      <c r="U47" s="2" t="inlineStr">
-        <is>
-          <t>2,41%</t>
-        </is>
-      </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>5,58%</t>
+          <t>5,45%</t>
         </is>
       </c>
     </row>
@@ -5720,47 +5720,47 @@
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>1814</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>5589</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>2,08%</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>6,41%</t>
+        </is>
+      </c>
+      <c r="J48" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D48" s="2" t="inlineStr">
-        <is>
-          <t>729</t>
-        </is>
-      </c>
-      <c r="E48" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F48" s="2" t="inlineStr">
-        <is>
-          <t>3728</t>
-        </is>
-      </c>
-      <c r="G48" s="2" t="inlineStr">
-        <is>
-          <t>1,15%</t>
-        </is>
-      </c>
-      <c r="H48" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="I48" s="2" t="inlineStr">
-        <is>
-          <t>5,87%</t>
-        </is>
-      </c>
-      <c r="J48" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>1688</t>
+          <t>817</t>
         </is>
       </c>
       <c r="L48" s="2" t="inlineStr">
@@ -5770,12 +5770,12 @@
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>6040</t>
+          <t>4142</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="O48" s="2" t="inlineStr">
@@ -5785,7 +5785,7 @@
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>7,43%</t>
+          <t>5,88%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -5795,17 +5795,17 @@
       </c>
       <c r="R48" s="2" t="inlineStr">
         <is>
-          <t>2417</t>
+          <t>2631</t>
         </is>
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>743</t>
+          <t>818</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>7341</t>
+          <t>7093</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
@@ -5815,12 +5815,12 @@
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>5,07%</t>
+          <t>4,5%</t>
         </is>
       </c>
     </row>
@@ -5833,72 +5833,72 @@
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>16186</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>10057</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>24220</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t>18,55%</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="inlineStr">
+        <is>
+          <t>11,53%</t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="inlineStr">
+        <is>
+          <t>27,76%</t>
+        </is>
+      </c>
+      <c r="J49" s="2" t="inlineStr">
+        <is>
           <t>17</t>
         </is>
       </c>
-      <c r="D49" s="2" t="inlineStr">
-        <is>
-          <t>12152</t>
-        </is>
-      </c>
-      <c r="E49" s="2" t="inlineStr">
-        <is>
-          <t>7250</t>
-        </is>
-      </c>
-      <c r="F49" s="2" t="inlineStr">
-        <is>
-          <t>18466</t>
-        </is>
-      </c>
-      <c r="G49" s="2" t="inlineStr">
-        <is>
-          <t>19,14%</t>
-        </is>
-      </c>
-      <c r="H49" s="2" t="inlineStr">
-        <is>
-          <t>11,42%</t>
-        </is>
-      </c>
-      <c r="I49" s="2" t="inlineStr">
-        <is>
-          <t>29,08%</t>
-        </is>
-      </c>
-      <c r="J49" s="2" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
       <c r="K49" s="2" t="inlineStr">
         <is>
-          <t>15587</t>
+          <t>13105</t>
         </is>
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>9830</t>
+          <t>8050</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>22920</t>
+          <t>20065</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
         <is>
-          <t>19,17%</t>
+          <t>18,62%</t>
         </is>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>12,09%</t>
+          <t>11,44%</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>28,19%</t>
+          <t>28,5%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -5908,32 +5908,32 @@
       </c>
       <c r="R49" s="2" t="inlineStr">
         <is>
-          <t>27739</t>
+          <t>29291</t>
         </is>
       </c>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>20075</t>
+          <t>21315</t>
         </is>
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>36662</t>
+          <t>39630</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
         <is>
-          <t>19,15%</t>
+          <t>18,58%</t>
         </is>
       </c>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>13,86%</t>
+          <t>13,52%</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>25,32%</t>
+          <t>25,14%</t>
         </is>
       </c>
     </row>
@@ -5946,72 +5946,72 @@
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>64329</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>55414</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>72225</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>73,73%</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>63,51%</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t>82,78%</t>
+        </is>
+      </c>
+      <c r="J50" s="2" t="inlineStr">
+        <is>
           <t>61</t>
         </is>
       </c>
-      <c r="D50" s="2" t="inlineStr">
-        <is>
-          <t>44120</t>
-        </is>
-      </c>
-      <c r="E50" s="2" t="inlineStr">
-        <is>
-          <t>36943</t>
-        </is>
-      </c>
-      <c r="F50" s="2" t="inlineStr">
-        <is>
-          <t>49956</t>
-        </is>
-      </c>
-      <c r="G50" s="2" t="inlineStr">
-        <is>
-          <t>69,48%</t>
-        </is>
-      </c>
-      <c r="H50" s="2" t="inlineStr">
-        <is>
-          <t>58,17%</t>
-        </is>
-      </c>
-      <c r="I50" s="2" t="inlineStr">
-        <is>
-          <t>78,67%</t>
-        </is>
-      </c>
-      <c r="J50" s="2" t="inlineStr">
-        <is>
-          <t>69</t>
-        </is>
-      </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>59338</t>
+          <t>48494</t>
         </is>
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>51462</t>
+          <t>39868</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>65854</t>
+          <t>55518</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
         <is>
-          <t>72,97%</t>
+          <t>68,89%</t>
         </is>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>63,29%</t>
+          <t>56,64%</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>80,99%</t>
+          <t>78,87%</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -6021,32 +6021,32 @@
       </c>
       <c r="R50" s="2" t="inlineStr">
         <is>
-          <t>103457</t>
+          <t>112823</t>
         </is>
       </c>
       <c r="S50" s="2" t="inlineStr">
         <is>
-          <t>93517</t>
+          <t>101069</t>
         </is>
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>112540</t>
+          <t>123058</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
         <is>
-          <t>71,44%</t>
+          <t>71,57%</t>
         </is>
       </c>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>64,58%</t>
+          <t>64,11%</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>77,71%</t>
+          <t>78,06%</t>
         </is>
       </c>
     </row>
@@ -6059,57 +6059,57 @@
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>87249</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>87249</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>87249</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I51" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J51" s="2" t="inlineStr">
+        <is>
           <t>87</t>
         </is>
       </c>
-      <c r="D51" s="2" t="inlineStr">
-        <is>
-          <t>63504</t>
-        </is>
-      </c>
-      <c r="E51" s="2" t="inlineStr">
-        <is>
-          <t>63504</t>
-        </is>
-      </c>
-      <c r="F51" s="2" t="inlineStr">
-        <is>
-          <t>63504</t>
-        </is>
-      </c>
-      <c r="G51" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H51" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I51" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J51" s="2" t="inlineStr">
-        <is>
-          <t>94</t>
-        </is>
-      </c>
       <c r="K51" s="2" t="inlineStr">
         <is>
-          <t>81315</t>
+          <t>70393</t>
         </is>
       </c>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>81315</t>
+          <t>70393</t>
         </is>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>81315</t>
+          <t>70393</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
@@ -6134,17 +6134,17 @@
       </c>
       <c r="R51" s="2" t="inlineStr">
         <is>
-          <t>144819</t>
+          <t>157642</t>
         </is>
       </c>
       <c r="S51" s="2" t="inlineStr">
         <is>
-          <t>144819</t>
+          <t>157642</t>
         </is>
       </c>
       <c r="T51" s="2" t="inlineStr">
         <is>
-          <t>144819</t>
+          <t>157642</t>
         </is>
       </c>
       <c r="U51" s="2" t="inlineStr">
@@ -6176,72 +6176,72 @@
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>4510</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>1705</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>9456</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t>1,67%</t>
+        </is>
+      </c>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t>0,63%</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="inlineStr">
+        <is>
+          <t>3,5%</t>
+        </is>
+      </c>
+      <c r="J52" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D52" s="2" t="inlineStr">
-        <is>
-          <t>5394</t>
-        </is>
-      </c>
-      <c r="E52" s="2" t="inlineStr">
-        <is>
-          <t>2112</t>
-        </is>
-      </c>
-      <c r="F52" s="2" t="inlineStr">
-        <is>
-          <t>11524</t>
-        </is>
-      </c>
-      <c r="G52" s="2" t="inlineStr">
-        <is>
-          <t>2,56%</t>
-        </is>
-      </c>
-      <c r="H52" s="2" t="inlineStr">
-        <is>
-          <t>1,0%</t>
-        </is>
-      </c>
-      <c r="I52" s="2" t="inlineStr">
-        <is>
-          <t>5,48%</t>
-        </is>
-      </c>
-      <c r="J52" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>4376</t>
+          <t>6729</t>
         </is>
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>1524</t>
+          <t>2730</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>9206</t>
+          <t>14377</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>7,28%</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -6251,32 +6251,32 @@
       </c>
       <c r="R52" s="2" t="inlineStr">
         <is>
-          <t>9770</t>
+          <t>11239</t>
         </is>
       </c>
       <c r="S52" s="2" t="inlineStr">
         <is>
-          <t>5103</t>
+          <t>6161</t>
         </is>
       </c>
       <c r="T52" s="2" t="inlineStr">
         <is>
-          <t>17603</t>
+          <t>20825</t>
         </is>
       </c>
       <c r="U52" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="V52" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>4,45%</t>
         </is>
       </c>
     </row>
@@ -6294,32 +6294,32 @@
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>5652</t>
+          <t>7082</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>2429</t>
+          <t>3075</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>10518</t>
+          <t>13926</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>5,16%</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
@@ -6329,32 +6329,32 @@
       </c>
       <c r="K53" s="2" t="inlineStr">
         <is>
-          <t>7200</t>
+          <t>6102</t>
         </is>
       </c>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>3299</t>
+          <t>2777</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>14624</t>
+          <t>11569</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>3,09%</t>
         </is>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>5,37%</t>
+          <t>5,85%</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -6364,32 +6364,32 @@
       </c>
       <c r="R53" s="2" t="inlineStr">
         <is>
-          <t>12852</t>
+          <t>13184</t>
         </is>
       </c>
       <c r="S53" s="2" t="inlineStr">
         <is>
-          <t>7471</t>
+          <t>7319</t>
         </is>
       </c>
       <c r="T53" s="2" t="inlineStr">
         <is>
-          <t>21086</t>
+          <t>21076</t>
         </is>
       </c>
       <c r="U53" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="V53" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>4,51%</t>
         </is>
       </c>
     </row>
@@ -6402,72 +6402,72 @@
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>3897</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>1445</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>8931</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t>1,44%</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t>0,54%</t>
+        </is>
+      </c>
+      <c r="I54" s="2" t="inlineStr">
+        <is>
+          <t>3,31%</t>
+        </is>
+      </c>
+      <c r="J54" s="2" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="D54" s="2" t="inlineStr">
-        <is>
-          <t>5576</t>
-        </is>
-      </c>
-      <c r="E54" s="2" t="inlineStr">
-        <is>
-          <t>2519</t>
-        </is>
-      </c>
-      <c r="F54" s="2" t="inlineStr">
-        <is>
-          <t>12080</t>
-        </is>
-      </c>
-      <c r="G54" s="2" t="inlineStr">
-        <is>
-          <t>2,65%</t>
-        </is>
-      </c>
-      <c r="H54" s="2" t="inlineStr">
-        <is>
-          <t>1,2%</t>
-        </is>
-      </c>
-      <c r="I54" s="2" t="inlineStr">
-        <is>
-          <t>5,74%</t>
-        </is>
-      </c>
-      <c r="J54" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
-          <t>3793</t>
+          <t>5788</t>
         </is>
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>1290</t>
+          <t>2417</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>8395</t>
+          <t>11506</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>5,82%</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -6477,22 +6477,22 @@
       </c>
       <c r="R54" s="2" t="inlineStr">
         <is>
-          <t>9369</t>
+          <t>9684</t>
         </is>
       </c>
       <c r="S54" s="2" t="inlineStr">
         <is>
-          <t>5204</t>
+          <t>5071</t>
         </is>
       </c>
       <c r="T54" s="2" t="inlineStr">
         <is>
-          <t>15826</t>
+          <t>16722</t>
         </is>
       </c>
       <c r="U54" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="V54" s="2" t="inlineStr">
@@ -6502,7 +6502,7 @@
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>3,58%</t>
         </is>
       </c>
     </row>
@@ -6515,72 +6515,72 @@
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>44215</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>33013</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>60148</t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="inlineStr">
+        <is>
+          <t>16,37%</t>
+        </is>
+      </c>
+      <c r="H55" s="2" t="inlineStr">
+        <is>
+          <t>12,22%</t>
+        </is>
+      </c>
+      <c r="I55" s="2" t="inlineStr">
+        <is>
+          <t>22,27%</t>
+        </is>
+      </c>
+      <c r="J55" s="2" t="inlineStr">
+        <is>
           <t>38</t>
         </is>
       </c>
-      <c r="D55" s="2" t="inlineStr">
-        <is>
-          <t>52104</t>
-        </is>
-      </c>
-      <c r="E55" s="2" t="inlineStr">
-        <is>
-          <t>26081</t>
-        </is>
-      </c>
-      <c r="F55" s="2" t="inlineStr">
-        <is>
-          <t>109831</t>
-        </is>
-      </c>
-      <c r="G55" s="2" t="inlineStr">
-        <is>
-          <t>24,76%</t>
-        </is>
-      </c>
-      <c r="H55" s="2" t="inlineStr">
-        <is>
-          <t>12,39%</t>
-        </is>
-      </c>
-      <c r="I55" s="2" t="inlineStr">
-        <is>
-          <t>52,18%</t>
-        </is>
-      </c>
-      <c r="J55" s="2" t="inlineStr">
-        <is>
-          <t>49</t>
-        </is>
-      </c>
       <c r="K55" s="2" t="inlineStr">
         <is>
-          <t>43592</t>
+          <t>29499</t>
         </is>
       </c>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>31683</t>
+          <t>21119</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>57711</t>
+          <t>41169</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
         <is>
-          <t>16,02%</t>
+          <t>14,93%</t>
         </is>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>11,64%</t>
+          <t>10,69%</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>21,21%</t>
+          <t>20,84%</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -6590,32 +6590,32 @@
       </c>
       <c r="R55" s="2" t="inlineStr">
         <is>
-          <t>95697</t>
+          <t>73714</t>
         </is>
       </c>
       <c r="S55" s="2" t="inlineStr">
         <is>
-          <t>68156</t>
+          <t>58318</t>
         </is>
       </c>
       <c r="T55" s="2" t="inlineStr">
         <is>
-          <t>165121</t>
+          <t>92530</t>
         </is>
       </c>
       <c r="U55" s="2" t="inlineStr">
         <is>
-          <t>19,83%</t>
+          <t>15,76%</t>
         </is>
       </c>
       <c r="V55" s="2" t="inlineStr">
         <is>
-          <t>14,12%</t>
+          <t>12,47%</t>
         </is>
       </c>
       <c r="W55" s="2" t="inlineStr">
         <is>
-          <t>34,21%</t>
+          <t>19,78%</t>
         </is>
       </c>
     </row>
@@ -6628,72 +6628,72 @@
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
+          <t>239</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>210396</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>193599</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>223193</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="inlineStr">
+        <is>
+          <t>77,9%</t>
+        </is>
+      </c>
+      <c r="H56" s="2" t="inlineStr">
+        <is>
+          <t>71,68%</t>
+        </is>
+      </c>
+      <c r="I56" s="2" t="inlineStr">
+        <is>
+          <t>82,63%</t>
+        </is>
+      </c>
+      <c r="J56" s="2" t="inlineStr">
+        <is>
           <t>209</t>
         </is>
       </c>
-      <c r="D56" s="2" t="inlineStr">
-        <is>
-          <t>141745</t>
-        </is>
-      </c>
-      <c r="E56" s="2" t="inlineStr">
-        <is>
-          <t>92958</t>
-        </is>
-      </c>
-      <c r="F56" s="2" t="inlineStr">
-        <is>
-          <t>167316</t>
-        </is>
-      </c>
-      <c r="G56" s="2" t="inlineStr">
-        <is>
-          <t>67,35%</t>
-        </is>
-      </c>
-      <c r="H56" s="2" t="inlineStr">
-        <is>
-          <t>44,17%</t>
-        </is>
-      </c>
-      <c r="I56" s="2" t="inlineStr">
-        <is>
-          <t>79,5%</t>
-        </is>
-      </c>
-      <c r="J56" s="2" t="inlineStr">
-        <is>
-          <t>239</t>
-        </is>
-      </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>213186</t>
+          <t>149470</t>
         </is>
       </c>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>197874</t>
+          <t>138189</t>
         </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>226249</t>
+          <t>160236</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
         <is>
-          <t>78,33%</t>
+          <t>75,65%</t>
         </is>
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>72,71%</t>
+          <t>69,94%</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>83,13%</t>
+          <t>81,1%</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
@@ -6703,32 +6703,32 @@
       </c>
       <c r="R56" s="2" t="inlineStr">
         <is>
-          <t>354931</t>
+          <t>359867</t>
         </is>
       </c>
       <c r="S56" s="2" t="inlineStr">
         <is>
-          <t>292251</t>
+          <t>338542</t>
         </is>
       </c>
       <c r="T56" s="2" t="inlineStr">
         <is>
-          <t>382548</t>
+          <t>377405</t>
         </is>
       </c>
       <c r="U56" s="2" t="inlineStr">
         <is>
-          <t>73,54%</t>
+          <t>76,95%</t>
         </is>
       </c>
       <c r="V56" s="2" t="inlineStr">
         <is>
-          <t>60,56%</t>
+          <t>72,39%</t>
         </is>
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>79,26%</t>
+          <t>80,7%</t>
         </is>
       </c>
     </row>
@@ -6741,57 +6741,57 @@
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
+          <t>307</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>270100</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>270100</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>270100</t>
+        </is>
+      </c>
+      <c r="G57" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H57" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I57" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J57" s="2" t="inlineStr">
+        <is>
           <t>270</t>
         </is>
       </c>
-      <c r="D57" s="2" t="inlineStr">
-        <is>
-          <t>210472</t>
-        </is>
-      </c>
-      <c r="E57" s="2" t="inlineStr">
-        <is>
-          <t>210472</t>
-        </is>
-      </c>
-      <c r="F57" s="2" t="inlineStr">
-        <is>
-          <t>210472</t>
-        </is>
-      </c>
-      <c r="G57" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H57" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I57" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J57" s="2" t="inlineStr">
-        <is>
-          <t>307</t>
-        </is>
-      </c>
       <c r="K57" s="2" t="inlineStr">
         <is>
-          <t>272147</t>
+          <t>197588</t>
         </is>
       </c>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>272147</t>
+          <t>197588</t>
         </is>
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>272147</t>
+          <t>197588</t>
         </is>
       </c>
       <c r="N57" s="2" t="inlineStr">
@@ -6816,17 +6816,17 @@
       </c>
       <c r="R57" s="2" t="inlineStr">
         <is>
-          <t>482619</t>
+          <t>467688</t>
         </is>
       </c>
       <c r="S57" s="2" t="inlineStr">
         <is>
-          <t>482619</t>
+          <t>467688</t>
         </is>
       </c>
       <c r="T57" s="2" t="inlineStr">
         <is>
-          <t>482619</t>
+          <t>467688</t>
         </is>
       </c>
       <c r="U57" s="2" t="inlineStr">
